--- a/artfynd/A 9573-2023 artfynd.xlsx
+++ b/artfynd/A 9573-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9573-2023 artfynd.xlsx
+++ b/artfynd/A 9573-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111525235</v>
+        <v>111525203</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404485.2245768273</v>
+        <v>404648</v>
       </c>
       <c r="R2" t="n">
-        <v>6706757.647421388</v>
+        <v>6707016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111525223</v>
+        <v>112243565</v>
       </c>
       <c r="B3" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404637.0659126193</v>
+        <v>404459</v>
       </c>
       <c r="R3" t="n">
-        <v>6706784.214121711</v>
+        <v>6706753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111525224</v>
+        <v>112243563</v>
       </c>
       <c r="B4" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Värsjön, väst, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404619.9854206198</v>
+        <v>404744</v>
       </c>
       <c r="R4" t="n">
-        <v>6706773.322858612</v>
+        <v>6707083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,31 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111525233</v>
+        <v>111525226</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404540.9329893424</v>
+        <v>404617</v>
       </c>
       <c r="R5" t="n">
-        <v>6706716.233959051</v>
+        <v>6706771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111525226</v>
+        <v>111525233</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404616.9589749529</v>
+        <v>404541</v>
       </c>
       <c r="R6" t="n">
-        <v>6706770.937089294</v>
+        <v>6706716</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111525238</v>
+        <v>111525235</v>
       </c>
       <c r="B7" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404495.4563026094</v>
+        <v>404485</v>
       </c>
       <c r="R7" t="n">
-        <v>6706677.491168984</v>
+        <v>6706757</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2023-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112243594</v>
+        <v>111525236</v>
       </c>
       <c r="B8" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1383,14 +1288,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404742</v>
+        <v>404472</v>
       </c>
       <c r="R8" t="n">
-        <v>6706992</v>
+        <v>6706721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,31 +1342,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112243573</v>
+        <v>111525237</v>
       </c>
       <c r="B9" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1485,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404477</v>
+        <v>404473</v>
       </c>
       <c r="R9" t="n">
-        <v>6706766</v>
+        <v>6706723</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,31 +1439,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112243569</v>
+        <v>111525238</v>
       </c>
       <c r="B10" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1587,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404751</v>
+        <v>404495</v>
       </c>
       <c r="R10" t="n">
-        <v>6707073</v>
+        <v>6706678</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,31 +1536,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112243589</v>
+        <v>111525239</v>
       </c>
       <c r="B11" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1689,14 +1579,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404762</v>
+        <v>404508</v>
       </c>
       <c r="R11" t="n">
-        <v>6707097</v>
+        <v>6706652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,31 +1633,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112243588</v>
+        <v>111525240</v>
       </c>
       <c r="B12" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1791,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väst Värsjön, Vrm</t>
+          <t>Värsjön, väst, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404452</v>
+        <v>404510</v>
       </c>
       <c r="R12" t="n">
-        <v>6706739</v>
+        <v>6706626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,31 +1730,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112243600</v>
+        <v>112243569</v>
       </c>
       <c r="B13" t="n">
-        <v>77689</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1897,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404725</v>
+        <v>404751</v>
       </c>
       <c r="R13" t="n">
-        <v>6707036</v>
+        <v>6707072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112243563</v>
+        <v>112243573</v>
       </c>
       <c r="B14" t="n">
-        <v>89614</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404744</v>
+        <v>404477</v>
       </c>
       <c r="R14" t="n">
-        <v>6707084</v>
+        <v>6706766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112243565</v>
+        <v>112243588</v>
       </c>
       <c r="B15" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404459</v>
+        <v>404451</v>
       </c>
       <c r="R15" t="n">
-        <v>6706753</v>
+        <v>6706739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112552453</v>
+        <v>112243589</v>
       </c>
       <c r="B16" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2199,14 +2064,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sydväst Skarptjärnen, Vrm</t>
+          <t>Väst Värsjön, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404648</v>
+        <v>404762</v>
       </c>
       <c r="R16" t="n">
-        <v>6706779</v>
+        <v>6707097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,15 +2118,597 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112243594</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Väst Värsjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>404743</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706991</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112243600</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Väst Värsjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>404725</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6707036</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112552453</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sydväst Skarptjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>404648</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706778</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111525223</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>404637</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706784</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111525234</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>404542</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706754</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111525224</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Värsjön, väst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>404620</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6706773</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9573-2023 artfynd.xlsx
+++ b/artfynd/A 9573-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243565</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243563</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525226</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525233</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525235</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525237</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525238</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525239</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525240</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243569</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243573</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243588</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243594</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243600</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552453</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525223</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525234</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,8 +2814,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111525224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>